--- a/OUTPUT/RealizeReports/Tonni.xlsx
+++ b/OUTPUT/RealizeReports/Tonni.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tonni" displayName="Tonni" ref="A1:Y11" headerRowCount="1">
-  <autoFilter ref="A1:Y11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tonni" displayName="Tonni" ref="A1:Y15" headerRowCount="1">
+  <autoFilter ref="A1:Y15"/>
   <tableColumns count="25">
     <tableColumn id="1" name="SL"/>
     <tableColumn id="2" name="LC_Factory"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>44498</v>
+        <v>39303</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -624,39 +624,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>PEPE JEANS SL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MGL/23/749</t>
+          <t>2400875</t>
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45204</v>
+        <v>45307</v>
       </c>
       <c r="G2" t="n">
-        <v>99066</v>
+        <v>4831</v>
       </c>
       <c r="H2" t="n">
-        <v>480570.44</v>
+        <v>62709.44</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MGNFL-2</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>40137</v>
+        <v>4831</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>45292.3896875</v>
+        <v>45308.72825231482</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>45226</v>
+        <v>45312</v>
       </c>
       <c r="M2" t="n">
-        <v>9807.559999999999</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PT Portugal</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -678,11 +678,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>FDBC 07-3816-23</t>
+          <t>FDBC/0355/2024</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>45229</v>
+        <v>45316</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>42909</v>
+        <v>17197</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -719,65 +719,65 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>PEPE JEANS SL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2314794</t>
+          <t>2605767</t>
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45209</v>
+        <v>46161</v>
       </c>
       <c r="G3" t="n">
-        <v>332</v>
+        <v>1013</v>
       </c>
       <c r="H3" t="n">
-        <v>1610.53</v>
+        <v>15298.97</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MGNFL-2</t>
+          <t>MGNSL</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>152</v>
+        <v>1013</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>45232.4321875</v>
+        <v>46166.71159722222</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>45226</v>
+        <v>46177</v>
       </c>
       <c r="M3" t="n">
-        <v>32.87</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>EXIM</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> $1,610.53 </t>
+          <t>15298.97</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>45358</v>
+        <v>46198</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>28012</v>
+        <v>26362</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -819,31 +819,31 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2400875</t>
+          <t>2606245</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45307</v>
+        <v>46166</v>
       </c>
       <c r="G4" t="n">
-        <v>4831</v>
+        <v>3441</v>
       </c>
       <c r="H4" t="n">
-        <v>62709.44</v>
+        <v>18581.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>MGNSL</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4831</v>
+        <v>3441</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>45308.72825231482</v>
+        <v>46166.6172337963</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>45312</v>
+        <v>46186</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -868,11 +868,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>FDBC/0355/2024</t>
+          <t>39649.70</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>45316</v>
+        <v>46194</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7220</v>
+        <v>27682</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -914,17 +914,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2605767</t>
+          <t>2606246</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46161</v>
+        <v>46166</v>
       </c>
       <c r="G5" t="n">
-        <v>1013</v>
+        <v>3582</v>
       </c>
       <c r="H5" t="n">
-        <v>15298.97</v>
+        <v>21068.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1013</v>
+        <v>3582</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46166.71159722222</v>
+        <v>46166.6172337963</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46177</v>
+        <v>46186</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -948,26 +948,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EXIM</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>15298.97</t>
+          <t>39649.70</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>46198</v>
+        <v>46194</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5401</v>
+        <v>29353</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2606245</t>
+          <t>2609039</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46166</v>
+        <v>46242</v>
       </c>
       <c r="G6" t="n">
-        <v>3441</v>
+        <v>7292</v>
       </c>
       <c r="H6" t="n">
-        <v>18581.4</v>
+        <v>37958.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3441</v>
+        <v>7292</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46166.6172337963</v>
+        <v>46245.46981481482</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46186</v>
+        <v>46250</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1058,11 +1058,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>39649.70</t>
+          <t>127033.57</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>46194</v>
+        <v>46264</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>21496</v>
+        <v>25872</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1099,36 +1099,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PEPE JEANS SL</t>
+          <t>ZXY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2606246</t>
+          <t>2609146</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46166</v>
+        <v>46245</v>
       </c>
       <c r="G7" t="n">
-        <v>3582</v>
+        <v>1815</v>
       </c>
       <c r="H7" t="n">
-        <v>21068.3</v>
+        <v>9183.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MGNSL</t>
+          <t>MGNFL-2</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3582</v>
+        <v>1815</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46166.6172337963</v>
+        <v>46248.84018518519</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46186</v>
+        <v>46261</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1143,21 +1143,21 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>EXIM</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>39649.70</t>
+          <t>3321.45</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>46194</v>
+        <v>46285</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>48726</v>
+        <v>21868</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1194,36 +1194,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PEPE JEANS SL</t>
+          <t>Fashion Fleet Clothing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2609039</t>
+          <t>2609277</t>
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46242</v>
+        <v>46247</v>
       </c>
       <c r="G8" t="n">
-        <v>7292</v>
+        <v>3697</v>
       </c>
       <c r="H8" t="n">
-        <v>37958.5</v>
+        <v>17513.79</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MGNSL</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7292</v>
+        <v>3697</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46245.46981481482</v>
+        <v>46258</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46250</v>
+        <v>46270</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1233,26 +1233,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>EXIM</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>127033.57</t>
+          <t>19609.67</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>46264</v>
+        <v>46289</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>50634</v>
+        <v>8486</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1289,22 +1289,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>EL CORTE INGLES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2609134</t>
+          <t>2609437</t>
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="G9" t="n">
-        <v>33549</v>
+        <v>237</v>
       </c>
       <c r="H9" t="n">
-        <v>149282.03</v>
+        <v>1208.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>33549</v>
+        <v>237</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="M9" t="n">
-        <v>3046.57</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1338,16 +1338,16 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>OBL</t>
+          <t>EXIM</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>149282.03</t>
+          <t>27268.08</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>46274</v>
+        <v>46286</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>34583</v>
+        <v>4338</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1384,22 +1384,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Assurer At Work Limited</t>
+          <t>EL CORTE INGLES</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2609476</t>
+          <t>2609431</t>
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="G10" t="n">
-        <v>9036</v>
+        <v>1639</v>
       </c>
       <c r="H10" t="n">
-        <v>28716.6</v>
+        <v>6998.53</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>9036</v>
+        <v>1639</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1428,21 +1428,21 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EXIM</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 32,278.16</t>
+          <t>27268.08</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>49271</v>
+        <v>11301</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1479,22 +1479,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Assurer At Work Limited</t>
+          <t>EL CORTE INGLES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2609610</t>
+          <t>2609429</t>
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="G11" t="n">
-        <v>1324</v>
+        <v>289</v>
       </c>
       <c r="H11" t="n">
-        <v>3561.56</v>
+        <v>1473.9</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1502,13 +1502,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1324</v>
+        <v>289</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46258</v>
+        <v>46256</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1523,21 +1523,21 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EXIM</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 32,278.16</t>
+          <t>27268.08</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1553,6 +1553,386 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>31084</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EL CORTE INGLES</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2609467</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1463</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11338.25</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1463</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>EXIM</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>27268.08</t>
+        </is>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9035</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fashion Fleet Clothing</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2609516</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="G13" t="n">
+        <v>302</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2095.88</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>302</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>NBL</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>19609.67</t>
+        </is>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3462</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EL CORTE INGLES</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2609871</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="G14" t="n">
+        <v>786</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6248.7</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>786</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>EXIM</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>27268.08</t>
+        </is>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>636</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PEPE JEANS SL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2610100</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="G15" t="n">
+        <v>823</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6666.3</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>823</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>46270.73099537037</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>EXIM</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>6666.30</t>
+        </is>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/OUTPUT/RealizeReports/Tonni.xlsx
+++ b/OUTPUT/RealizeReports/Tonni.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tonni" displayName="Tonni" ref="A1:Y15" headerRowCount="1">
-  <autoFilter ref="A1:Y15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tonni" displayName="Tonni" ref="A1:Y29" headerRowCount="1">
+  <autoFilter ref="A1:Y29"/>
   <tableColumns count="25">
     <tableColumn id="1" name="SL"/>
     <tableColumn id="2" name="LC_Factory"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39303</v>
+        <v>23154</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -624,39 +624,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PEPE JEANS SL</t>
+          <t>Springfield</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2400875</t>
+          <t>2314794</t>
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45307</v>
+        <v>45209</v>
       </c>
       <c r="G2" t="n">
-        <v>4831</v>
+        <v>332</v>
       </c>
       <c r="H2" t="n">
-        <v>62709.44</v>
+        <v>1610.53</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>MGNFL-2</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4831</v>
+        <v>152</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>45308.72825231482</v>
+        <v>45232.4321875</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>45312</v>
+        <v>45226</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>32.87</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -678,11 +678,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>FDBC/0355/2024</t>
+          <t xml:space="preserve"> $1,610.53 </t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>45316</v>
+        <v>45358</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17197</v>
+        <v>1229</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -724,31 +724,31 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2605767</t>
+          <t>2400875</t>
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46161</v>
+        <v>45307</v>
       </c>
       <c r="G3" t="n">
-        <v>1013</v>
+        <v>4831</v>
       </c>
       <c r="H3" t="n">
-        <v>15298.97</v>
+        <v>62709.44</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MGNSL</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1013</v>
+        <v>4831</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46166.71159722222</v>
+        <v>45308.72825231482</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46177</v>
+        <v>45312</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -758,26 +758,26 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EXIM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>15298.97</t>
+          <t>FDBC/0355/2024</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>46198</v>
+        <v>45316</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>26362</v>
+        <v>9641</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -819,17 +819,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2606245</t>
+          <t>2601191</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46166</v>
+        <v>46042</v>
       </c>
       <c r="G4" t="n">
-        <v>3441</v>
+        <v>192</v>
       </c>
       <c r="H4" t="n">
-        <v>18581.4</v>
+        <v>1574.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3441</v>
+        <v>192</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46166.6172337963</v>
+        <v>46050.50475694444</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46186</v>
+        <v>46050</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -853,12 +853,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -868,11 +868,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>39649.70</t>
+          <t>1574.40</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>46194</v>
+        <v>46295</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>27682</v>
+        <v>20021</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -914,17 +914,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2606246</t>
+          <t>2605767</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46166</v>
+        <v>46161</v>
       </c>
       <c r="G5" t="n">
-        <v>3582</v>
+        <v>1013</v>
       </c>
       <c r="H5" t="n">
-        <v>21068.3</v>
+        <v>15298.97</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3582</v>
+        <v>1013</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46166.6172337963</v>
+        <v>46166.71159722222</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46186</v>
+        <v>46177</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -948,26 +948,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>EXIM</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>39649.70</t>
+          <t>15298.97</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>46194</v>
+        <v>46198</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>29353</v>
+        <v>3376</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2609039</t>
+          <t>2606245</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46242</v>
+        <v>46166</v>
       </c>
       <c r="G6" t="n">
-        <v>7292</v>
+        <v>3441</v>
       </c>
       <c r="H6" t="n">
-        <v>37958.5</v>
+        <v>18581.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7292</v>
+        <v>3441</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46245.46981481482</v>
+        <v>46166.6172337963</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46250</v>
+        <v>46186</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1058,11 +1058,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>127033.57</t>
+          <t>39649.70</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>46264</v>
+        <v>46194</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>25872</v>
+        <v>20385</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1099,36 +1099,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ZXY</t>
+          <t>PEPE JEANS SL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2609146</t>
+          <t>2606246</t>
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46245</v>
+        <v>46166</v>
       </c>
       <c r="G7" t="n">
-        <v>1815</v>
+        <v>3582</v>
       </c>
       <c r="H7" t="n">
-        <v>9183.9</v>
+        <v>21068.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MGNFL-2</t>
+          <t>MGNSL</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1815</v>
+        <v>3582</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46248.84018518519</v>
+        <v>46166.6172337963</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46261</v>
+        <v>46186</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1143,21 +1143,21 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EXIM</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3321.45</t>
+          <t>39649.70</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>46285</v>
+        <v>46194</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21868</v>
+        <v>10080</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1199,32 +1199,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2609277</t>
+          <t>2608925</t>
         </is>
       </c>
       <c r="F8" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12564</v>
+      </c>
+      <c r="H8" t="n">
+        <v>69982.02</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>12564</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L8" s="1" t="n">
         <v>46247</v>
       </c>
-      <c r="G8" t="n">
-        <v>3697</v>
-      </c>
-      <c r="H8" t="n">
-        <v>17513.79</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>MGL</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>3697</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>46270</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -1248,11 +1248,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>19609.67</t>
+          <t xml:space="preserve">$76,334.51	</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8486</v>
+        <v>9811</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1294,31 +1294,31 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2609437</t>
+          <t>2609027</t>
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46252</v>
+        <v>46238</v>
       </c>
       <c r="G9" t="n">
-        <v>237</v>
+        <v>21398</v>
       </c>
       <c r="H9" t="n">
-        <v>1208.7</v>
+        <v>162838.78</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>MGNFL-2</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>237</v>
+        <v>21398</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46253</v>
+        <v>46238.40606481482</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46262</v>
+        <v>46246</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1343,11 +1343,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>27268.08</t>
+          <t>165443.72</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>46286</v>
+        <v>46296</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4338</v>
+        <v>14317</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1384,36 +1384,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EL CORTE INGLES</t>
+          <t>PEPE JEANS SL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2609431</t>
+          <t>2609039</t>
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>46252</v>
+        <v>46242</v>
       </c>
       <c r="G10" t="n">
-        <v>1639</v>
+        <v>7292</v>
       </c>
       <c r="H10" t="n">
-        <v>6998.53</v>
+        <v>37958.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>MGNSL</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1639</v>
+        <v>7292</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46253</v>
+        <v>46245.46981481482</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>46262</v>
+        <v>46250</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1438,11 +1438,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>27268.08</t>
+          <t>127033.57</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>46286</v>
+        <v>46264</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11301</v>
+        <v>34277</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1479,36 +1479,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EL CORTE INGLES</t>
+          <t>ZXY</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2609429</t>
+          <t>2609146</t>
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>46252</v>
+        <v>46245</v>
       </c>
       <c r="G11" t="n">
-        <v>289</v>
+        <v>1815</v>
       </c>
       <c r="H11" t="n">
-        <v>1473.9</v>
+        <v>9183.9</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>MGNFL-2</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>289</v>
+        <v>1815</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46256</v>
+        <v>46248.84018518519</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1523,21 +1523,21 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>EXIM</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>27268.08</t>
+          <t>3321.45</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>31084</v>
+        <v>18216</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1579,17 +1579,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2609467</t>
+          <t>2609154</t>
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>46254</v>
+        <v>46246</v>
       </c>
       <c r="G12" t="n">
-        <v>1463</v>
+        <v>1500</v>
       </c>
       <c r="H12" t="n">
-        <v>11338.25</v>
+        <v>8625</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1463</v>
+        <v>1500</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46256</v>
+        <v>46246.71456018519</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46263</v>
+        <v>46257</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1618,21 +1618,21 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>EXIM</t>
+          <t>OBL</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>27268.08</t>
+          <t>83279.33</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>46286</v>
+        <v>46296</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9035</v>
+        <v>17634</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1669,37 +1669,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fashion Fleet Clothing</t>
+          <t>EL CORTE INGLES</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2609516</t>
+          <t>2609151</t>
         </is>
       </c>
       <c r="F13" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1056</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8368.799999999999</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1056</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>46251.64223379629</v>
+      </c>
+      <c r="L13" s="1" t="n">
         <v>46254</v>
       </c>
-      <c r="G13" t="n">
-        <v>302</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2095.88</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MGL</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>302</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>46258</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>46263</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1708,26 +1708,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>OBL</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>19609.67</t>
+          <t>83279.33</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3462</v>
+        <v>42345</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1769,17 +1769,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2609871</t>
+          <t>2609152</t>
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>46262</v>
+        <v>46246</v>
       </c>
       <c r="G14" t="n">
-        <v>786</v>
+        <v>528</v>
       </c>
       <c r="H14" t="n">
-        <v>6248.7</v>
+        <v>4092</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>786</v>
+        <v>528</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46265</v>
+        <v>46251.64223379629</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46268</v>
+        <v>46254</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Air</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1813,16 +1813,16 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>EXIM</t>
+          <t>OBL</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>27268.08</t>
+          <t>83279.33</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>46286</v>
+        <v>46296</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>636</v>
+        <v>17712</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1859,36 +1859,36 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PEPE JEANS SL</t>
+          <t>EL CORTE INGLES</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2610100</t>
+          <t>2609166</t>
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>46268</v>
+        <v>46246</v>
       </c>
       <c r="G15" t="n">
-        <v>823</v>
+        <v>1200</v>
       </c>
       <c r="H15" t="n">
-        <v>6666.3</v>
+        <v>9420</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MGNSL</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>823</v>
+        <v>1200</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46270.73099537037</v>
+        <v>46246.4062962963</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1903,21 +1903,21 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>EXIM</t>
+          <t>OBL</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>6666.30</t>
+          <t>83279.33</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>46287</v>
+        <v>46296</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1933,6 +1933,1336 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>38554</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EL CORTE INGLES</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2609164</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1900</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11590</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1900</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>46246.4062962963</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>OBL</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>83279.33</t>
+        </is>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>42956</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EL CORTE INGLES</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2609156</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1700</v>
+      </c>
+      <c r="H17" t="n">
+        <v>9775</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1700</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>46246.71456018519</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>OBL</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>83279.33</t>
+        </is>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>42400</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fashion Fleet Clothing</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2609277</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3697</v>
+      </c>
+      <c r="H18" t="n">
+        <v>17513.79</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>3697</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>46270</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>NBL</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>19609.67</t>
+        </is>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>27790</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EL CORTE INGLES</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2609279</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G19" t="n">
+        <v>651</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3678.15</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>651</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>OBL</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>83279.33</t>
+        </is>
+      </c>
+      <c r="S19" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>21968</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EL CORTE INGLES</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2609463</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="G20" t="n">
+        <v>420</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3679.2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>420</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>OBL</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>83279.33</t>
+        </is>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8933</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fashion Fleet Clothing</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2609516</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="G21" t="n">
+        <v>302</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2095.88</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>302</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>NBL</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>19609.67</t>
+        </is>
+      </c>
+      <c r="S21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>549</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EL CORTE INGLES</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2609774</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="G22" t="n">
+        <v>650</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4628</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>650</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>46264</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>OBL</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>83279.33</t>
+        </is>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>15494</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EL CORTE INGLES</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2609870</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="G23" t="n">
+        <v>960</v>
+      </c>
+      <c r="H23" t="n">
+        <v>10560</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MGNFL-2</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>960</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>46263.79490740741</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>OBL</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>83279.33</t>
+        </is>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>29175</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EL CORTE INGLES</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2609876</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>46264</v>
+      </c>
+      <c r="G24" t="n">
+        <v>334</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1816</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>334</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>OBL</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>83279.33</t>
+        </is>
+      </c>
+      <c r="S24" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3929</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EL CORTE INGLES</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2610002</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G25" t="n">
+        <v>225</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2409.75</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>225</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>46271</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>OBL</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>83279.33</t>
+        </is>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>16511</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EL CORTE INGLES</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2610001</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G26" t="n">
+        <v>433</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4637.43</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>433</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>OBL</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>83279.33</t>
+        </is>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>38660</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PEPE JEANS SL</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2610100</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="G27" t="n">
+        <v>823</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6666.3</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MGNSL</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>823</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>46270.73099537037</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>EXIM</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>6666.30</t>
+        </is>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>42492</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LPP SA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2610569</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4192</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10857.28</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MGNFL-2</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>4192</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>46285.49989583333</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>NBL</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>25590.20</t>
+        </is>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>32293</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Woven</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LPP SA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2610660</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4778</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15002.92</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>MGNFL-2</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>4778</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>46285.49989583333</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sea</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>NBL</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>25590.20</t>
+        </is>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Realize Pending</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
